--- a/public/assets/template-excel/kabel-fo.xlsx
+++ b/public/assets/template-excel/kabel-fo.xlsx
@@ -11,18 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>SEGMEN</t>
-  </si>
-  <si>
-    <t>KLASIFIKASI</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>LETAK KABEL</t>
   </si>
   <si>
     <t>JUMLAH CORE</t>
+  </si>
+  <si>
+    <t>JUMLAH CORE TERPAKAI</t>
   </si>
   <si>
     <t>JALUR KABEL</t>
@@ -59,13 +56,13 @@
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF000000"/>
+      <sz val="8.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -89,15 +86,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -312,13 +312,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="14.0"/>
-    <col customWidth="1" min="6" max="6" width="21.88"/>
-    <col customWidth="1" min="7" max="7" width="22.75"/>
-    <col customWidth="1" min="8" max="8" width="22.5"/>
-    <col customWidth="1" min="9" max="9" width="23.63"/>
-    <col customWidth="1" min="10" max="10" width="17.88"/>
-    <col customWidth="1" min="11" max="11" width="19.0"/>
+    <col customWidth="1" min="3" max="3" width="21.13"/>
+    <col customWidth="1" min="4" max="4" width="15.13"/>
+    <col customWidth="1" min="5" max="5" width="22.5"/>
+    <col customWidth="1" min="6" max="6" width="20.88"/>
+    <col customWidth="1" min="7" max="7" width="19.63"/>
+    <col customWidth="1" min="8" max="8" width="20.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,12 +348,10 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="K1" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/public/assets/template-excel/kabel-fo.xlsx
+++ b/public/assets/template-excel/kabel-fo.xlsx
@@ -11,7 +11,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>CABANG</t>
+  </si>
+  <si>
+    <t>SEGMEN</t>
+  </si>
+  <si>
+    <t>KLASIFIKASI</t>
+  </si>
   <si>
     <t>LETAK KABEL</t>
   </si>
@@ -61,6 +70,7 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -86,18 +96,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,31 +343,39 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
